--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251001_170551.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251001_170551.xlsx
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251001_170551.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251001_170551.xlsx
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251001_170551.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251001_170551.xlsx
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251001_170551.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251001_170551.xlsx
@@ -7238,7 +7238,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251001_170551.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251001_170551.xlsx
@@ -7238,7 +7238,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251001_170551.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251001_170551.xlsx
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
